--- a/src/fastcashflow/sample_data/sample_basis.xlsx
+++ b/src/fastcashflow/sample_data/sample_basis.xlsx
@@ -821,7 +821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -832,60 +832,70 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>product_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>channel_code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>channel_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>mortality_table</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>lapse_table</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>waiver_table</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>discount_table</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>inflation_table</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ra_confidence</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>mortality_cv</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>morbidity_cv</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>state_model</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>surrender_value_table</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>expense_table</t>
         </is>
@@ -897,41 +907,41 @@
           <t>defaults</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>MORTALITY_STD</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>WAIVER_STD</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>DISCOUNT_STD</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>INFL_BASE</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.75</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>0.1</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.12</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>WAIVER</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>SURRENDER_STD</t>
         </is>
@@ -945,15 +955,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>정기보험</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>FC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>전속설계사</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>LAPSE_FC</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>EXP_TE_FC</t>
         </is>
@@ -967,15 +987,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>정기보험</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>GA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>법인대리점</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>LAPSE_GA</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>EXP_TE_GA</t>
         </is>
@@ -989,15 +1019,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>건강보험</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>FC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>전속설계사</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>LAPSE_FC</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>EXP_HE_FC</t>
         </is>
@@ -1011,15 +1051,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>건강보험</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>GA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>법인대리점</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>LAPSE_GA</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>EXP_HE_GA</t>
         </is>
@@ -1033,15 +1083,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>건강보험</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>TM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>텔레마케팅</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>LAPSE_GA</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>EXP_HE_TM</t>
         </is>
@@ -1055,15 +1115,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>종신보험</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>FC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>전속설계사</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>LAPSE_FC</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>EXP_WH_FC</t>
         </is>
@@ -1077,15 +1147,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>종신보험</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>GA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>법인대리점</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>LAPSE_GA</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>EXP_WH_GA</t>
         </is>

--- a/src/fastcashflow/sample_data/sample_basis.xlsx
+++ b/src/fastcashflow/sample_data/sample_basis.xlsx
@@ -505,7 +505,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>defaults</t>
+          <t>_DEFAULTS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/src/fastcashflow/sample_data/sample_basis.xlsx
+++ b/src/fastcashflow/sample_data/sample_basis.xlsx
@@ -422,81 +422,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>product_code</t>
+          <t>product</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>product_name</t>
+          <t>channel</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>channel_code</t>
+          <t>mortality_table</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>channel_name</t>
+          <t>lapse_table</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>mortality_table</t>
+          <t>waiver_table</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>lapse_table</t>
+          <t>discount_table</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>waiver_table</t>
+          <t>inflation_table</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>discount_table</t>
+          <t>ra_confidence</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>inflation_table</t>
+          <t>mortality_cv</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>ra_confidence</t>
+          <t>morbidity_cv</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>mortality_cv</t>
+          <t>state_model</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>morbidity_cv</t>
+          <t>surrender_value_table</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
-        <is>
-          <t>state_model</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>surrender_value_table</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
         <is>
           <t>expense_table</t>
         </is>
@@ -508,36 +498,36 @@
           <t>_DEFAULTS</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MORTALITY_STD</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MORTALITY_STD</t>
+          <t>WAIVER_STD</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>DISCOUNT_STD</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>WAIVER_STD</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>DISCOUNT_STD</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
           <t>INFL_BASE</t>
         </is>
       </c>
+      <c r="H2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1</v>
+      </c>
       <c r="J2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L2" t="n">
         <v>0.12</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>WAIVER</t>
         </is>
@@ -551,30 +541,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>정기보험</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
           <t>FC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>전속설계사</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
           <t>LAPSE_TERM_FC</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>SURR_TERM</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>SURR_TERM</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>EXP_TE_FC</t>
         </is>
@@ -588,30 +568,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>정기보험</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
           <t>GA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>법인대리점</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
           <t>LAPSE_TERM_GA</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>SURR_TERM</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>SURR_TERM</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>EXP_TE_GA</t>
         </is>
@@ -625,30 +595,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>건강보험</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
           <t>FC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>전속설계사</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
           <t>LAPSE_HEALTH_FC</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>SURR_HEALTH</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>SURR_HEALTH</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>EXP_HE_FC</t>
         </is>
@@ -662,30 +622,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>건강보험</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
           <t>GA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>법인대리점</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
           <t>LAPSE_HEALTH_GA</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>SURR_HEALTH</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>SURR_HEALTH</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>EXP_HE_GA</t>
         </is>
@@ -699,30 +649,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>건강보험</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
           <t>TM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>텔레마케팅</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
           <t>LAPSE_HEALTH_GA</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>SURR_HEALTH</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>SURR_HEALTH</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>EXP_HE_TM</t>
         </is>
@@ -736,30 +676,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>종신보험</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
           <t>FC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>전속설계사</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
           <t>LAPSE_WHOLE_FC</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>SURR_WHOLE</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>SURR_WHOLE</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>EXP_WH_FC</t>
         </is>
@@ -773,30 +703,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>종신보험</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
           <t>GA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>법인대리점</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
           <t>LAPSE_WHOLE_GA</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>SURR_WHOLE</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>SURR_WHOLE</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>EXP_WH_GA</t>
         </is>
@@ -863,7 +783,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>coverage_code</t>
+          <t>coverage</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">

--- a/src/fastcashflow/sample_data/sample_basis.xlsx
+++ b/src/fastcashflow/sample_data/sample_basis.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>EXP_TE_FC</t>
+          <t>EXPENSE_TERM_FC</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>EXP_TE_GA</t>
+          <t>EXPENSE_TERM_GA</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>EXP_HE_FC</t>
+          <t>EXPENSE_HEALTH_FC</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>EXP_HE_GA</t>
+          <t>EXPENSE_HEALTH_GA</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>EXP_HE_TM</t>
+          <t>EXPENSE_HEALTH_TM</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>EXP_WH_FC</t>
+          <t>EXPENSE_WHOLE_FC</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>EXP_WH_GA</t>
+          <t>EXPENSE_WHOLE_GA</t>
         </is>
       </c>
     </row>
@@ -75716,7 +75716,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EXP_TE_FC</t>
+          <t>EXPENSE_TERM_FC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -75736,7 +75736,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EXP_TE_FC</t>
+          <t>EXPENSE_TERM_FC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -75756,7 +75756,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EXP_TE_GA</t>
+          <t>EXPENSE_TERM_GA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -75776,7 +75776,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EXP_TE_GA</t>
+          <t>EXPENSE_TERM_GA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -75796,7 +75796,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EXP_HE_FC</t>
+          <t>EXPENSE_HEALTH_FC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -75816,7 +75816,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EXP_HE_FC</t>
+          <t>EXPENSE_HEALTH_FC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -75836,7 +75836,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EXP_HE_GA</t>
+          <t>EXPENSE_HEALTH_GA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -75856,7 +75856,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXP_HE_GA</t>
+          <t>EXPENSE_HEALTH_GA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -75876,7 +75876,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXP_HE_TM</t>
+          <t>EXPENSE_HEALTH_TM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -75896,7 +75896,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXP_HE_TM</t>
+          <t>EXPENSE_HEALTH_TM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -75916,7 +75916,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXP_WH_FC</t>
+          <t>EXPENSE_WHOLE_FC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -75936,7 +75936,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EXP_WH_FC</t>
+          <t>EXPENSE_WHOLE_FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -75956,7 +75956,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXP_WH_GA</t>
+          <t>EXPENSE_WHOLE_GA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -75976,7 +75976,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EXP_WH_GA</t>
+          <t>EXPENSE_WHOLE_GA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/src/fastcashflow/sample_data/sample_basis.xlsx
+++ b/src/fastcashflow/sample_data/sample_basis.xlsx
@@ -75699,12 +75699,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>expense_type</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>basis</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -75726,7 +75726,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>alpha_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -75746,7 +75746,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gamma_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -75766,7 +75766,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>alpha_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -75786,7 +75786,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gamma_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -75806,7 +75806,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>alpha_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -75826,7 +75826,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>gamma_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -75846,7 +75846,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>alpha_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -75866,7 +75866,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gamma_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -75886,7 +75886,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>alpha_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -75906,7 +75906,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gamma_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -75926,7 +75926,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>alpha_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -75946,7 +75946,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>gamma_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -75966,7 +75966,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>alpha_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -75986,7 +75986,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gamma_fixed</t>
+          <t>per_policy</t>
         </is>
       </c>
       <c r="D15" t="n">

--- a/src/fastcashflow/sample_data/sample_basis.xlsx
+++ b/src/fastcashflow/sample_data/sample_basis.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>WAIVER</t>
+          <t>ACTIVE_WAIVER</t>
         </is>
       </c>
     </row>

--- a/src/fastcashflow/sample_data/sample_basis.xlsx
+++ b/src/fastcashflow/sample_data/sample_basis.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>state_model</t>
+          <t>state_machine</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
